--- a/Capstone_Project/12_Assessment/Group-3_Final_Submission_Checklist.xlsx
+++ b/Capstone_Project/12_Assessment/Group-3_Final_Submission_Checklist.xlsx
@@ -747,12 +747,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7 of 8 coding tasks merged on GitHub and the Lecturer slots page is left</t>
+          <t>All 8 coding tasks merged on GitHub and the fixes after testing still need to be committed</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -768,12 +768,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GitHub branches and pull requests #1 to #4 and Chapter 4.8 still to write</t>
+          <t>Group-3_Git_Evidence.docx and screenshots (folder 10) and Chapter 4.8 (GitHub branches, commits and pull requests #1 to #7)</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -789,12 +789,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Test Plan and user testing with 5 students and 1 lecturer</t>
+          <t>Test Plan done and the tests passed after the fixes and user testing with 5 students and 1 lecturer still to do</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Chapter 5 and Requirements_Traceability_Matrix.xlsx</t>
+          <t>Chapter 5 with the survey and Requirements_Traceability_Matrix.xlsx (user test results still to add in Week 5)</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Demo Script backup video and demo laptop on Tue 27 Oct</t>
+          <t>Demo Script and slides drafted (folder 11) and the backup video is ready and the demo laptop check is on Tue 27 Oct</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>

--- a/Capstone_Project/12_Assessment/Group-3_Final_Submission_Checklist.xlsx
+++ b/Capstone_Project/12_Assessment/Group-3_Final_Submission_Checklist.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6</t>
+          <t>Chapter 6 section 6.4 answers the research questions with the survey results (the ease of use answer is updated after the Week 5 user testing)</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -873,12 +873,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6</t>
+          <t>Chapter 6 section 6.3 (to be updated with the test results and the Week 5 user testing)</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -894,12 +894,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6</t>
+          <t>Chapter 6 section 6.5</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6</t>
+          <t>Chapter 6 sections 6.6 and 6.7</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>

--- a/Capstone_Project/12_Assessment/Group-3_Final_Submission_Checklist.xlsx
+++ b/Capstone_Project/12_Assessment/Group-3_Final_Submission_Checklist.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Chapter 1 Problem Statement (Group-3_Week3.pdf)</t>
+          <t>Chapter 1 Problem Statement (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -542,7 +542,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Chapter 1 Research Aim (Group-3_Week3.pdf)</t>
+          <t>Chapter 1 Research Aim (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Chapter 1 Research Objectives (Group-3_Week3.pdf)</t>
+          <t>Chapter 1 Research Objectives (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Chapter 1 Research Questions (Group-3_Week3.pdf)</t>
+          <t>Chapter 1 Research Questions (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Chapter 2 and Appendix C Literature Review Matrix (Group-3_Week3.pdf)</t>
+          <t>Chapter 2 and Group-3_Literature_Review_Matrix.xlsx in folder 02 (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -626,7 +626,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Chapter 2 Research Gap (Group-3_Week3.pdf)</t>
+          <t>Chapter 2 Research Gap (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Chapter 3 (Group-3_Week3.pdf)</t>
+          <t>Chapter 3 (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Chapter 3 and Appendix D SRS (Group-3_Week3.pdf)</t>
+          <t>Chapter 3 and Group-3_Software_Requirements_Specification_SRS.docx in folder 03 (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Chapter 3 and Appendix D SRS (Group-3_Week3.pdf)</t>
+          <t>Chapter 3 and Group-3_Software_Requirements_Specification_SRS.docx in folder 03 (Group3_Final_Dissertation)</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>All 8 coding tasks merged on GitHub and the fixes after testing still need to be committed</t>
+          <t>All 8 coding tasks and the fixes from testing merged into main on GitHub</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -789,12 +789,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Test Plan done and the tests passed after the fixes and user testing with 5 students and 1 lecturer still to do</t>
+          <t>Test Plan and 36 test cases (35 pass) and user testing with 4 students and 2 lecturers on 28 Oct (Chapter 5 sections 5.2 and 5.6)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -831,12 +831,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Chapter 5 with the survey and Requirements_Traceability_Matrix.xlsx (user test results still to add in Week 5)</t>
+          <t>Chapter 5 sections 5.5 and 5.7 and Requirements_Traceability_Matrix.xlsx with the user testing in section 5.6</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -852,12 +852,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6 section 6.4 answers the research questions with the survey results (the ease of use answer is updated after the Week 5 user testing)</t>
+          <t>Chapter 6 section 6.4 answers all five research questions with the survey and the user testing</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -873,12 +873,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6 section 6.3 (to be updated with the test results and the Week 5 user testing)</t>
+          <t>Chapter 6 section 6.3 (objectives 1 to 3 achieved, 4 mostly and 5 partly achieved)</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6 sections 6.6 and 6.7</t>
+          <t>Chapter 6 section 6.6 Recommendations and Future Work</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -936,12 +936,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Reference list in Group-3_Week3.pdf and new sources to add</t>
+          <t>References list in Group3_Final_Dissertation (13 sources, Harvard style)</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Appendices A to E in Group-3_Week3.pdf</t>
+          <t>Appendices A to H in Group3_Final_Dissertation</t>
         </is>
       </c>
       <c r="E25" s="2" t="n"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Demo Script and slides drafted (folder 11) and the backup video is ready and the demo laptop check is on Tue 27 Oct</t>
+          <t>Demo Script and slides in folder 11, backup video ready, and MySQL and the booking emails checked on the demonstration laptop</t>
         </is>
       </c>
       <c r="E26" s="2" t="n"/>
